--- a/data/Baseline_Cover_TEMPLATE.xlsx
+++ b/data/Baseline_Cover_TEMPLATE.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9669A77F-0F6B-457B-AB70-BC156511B763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3953" yWindow="3953" windowWidth="24495" windowHeight="10522" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
+    <workbookView xWindow="57480" yWindow="22020" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -1508,15 +1508,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
@@ -1525,6 +1516,15 @@
     <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1723,20 +1723,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
     <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
